--- a/data/trans_camb/IP19C04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 18,95</t>
+          <t>-1,52; 18,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 15,48</t>
+          <t>-5,31; 15,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 4,39</t>
+          <t>-9,9; 3,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 1,85</t>
+          <t>-17,51; 1,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 1,05</t>
+          <t>-19,77; 0,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 5,91</t>
+          <t>-18,47; 3,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 7,77</t>
+          <t>-5,56; 8,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 4,17</t>
+          <t>-10,03; 4,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 1,85</t>
+          <t>-10,75; 1,11</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 825,44</t>
+          <t>-29,68; 924,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,38</t>
+          <t>-100,0; 77,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 102,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 314,32</t>
+          <t>-100,0; 95,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 155,98</t>
+          <t>-48,11; 172,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,3; 111,66</t>
+          <t>-86,31; 103,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,28; 67,33</t>
+          <t>-93,18; 44,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 4,17</t>
+          <t>-3,43; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,85</t>
+          <t>-4,11; 2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,92</t>
+          <t>-4,56; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 4,52</t>
+          <t>-3,85; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,35</t>
+          <t>-5,15; 1,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; -0,15</t>
+          <t>-6,47; -0,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,14</t>
+          <t>-2,51; 3,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,02</t>
+          <t>-3,88; 1,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 0,16</t>
+          <t>-4,57; -0,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 100,13</t>
+          <t>-44,94; 85,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 65,45</t>
+          <t>-50,82; 69,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 75,57</t>
+          <t>-59,0; 57,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 95,06</t>
+          <t>-46,52; 72,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 29,81</t>
+          <t>-64,0; 31,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,56; -0,42</t>
+          <t>-74,86; 1,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 64,51</t>
+          <t>-32,93; 63,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 21,49</t>
+          <t>-49,01; 22,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,23; 4,35</t>
+          <t>-59,04; -0,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 0,94</t>
+          <t>-8,98; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 3,13</t>
+          <t>-7,84; 3,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,04</t>
+          <t>-6,39; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 2,23</t>
+          <t>-9,16; 2,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 1,59</t>
+          <t>-9,47; 1,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 1,33</t>
+          <t>-9,4; 1,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,22</t>
+          <t>-7,37; 0,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 1,18</t>
+          <t>-6,76; 1,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 1,43</t>
+          <t>-6,17; 1,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 171,65</t>
+          <t>-100,0; 114,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 185,54</t>
+          <t>-88,54; 201,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,2; 202,46</t>
+          <t>-76,95; 162,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-93,4; 122,74</t>
+          <t>-87,92; 159,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 155,06</t>
+          <t>-100,0; 139,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,57; 81,87</t>
+          <t>-91,73; 97,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 18,17</t>
+          <t>-88,19; 24,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 50,78</t>
+          <t>-83,86; 47,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 48,42</t>
+          <t>-74,84; 52,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,54</t>
+          <t>-2,28; 3,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,24</t>
+          <t>-3,43; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,02</t>
+          <t>-3,96; 1,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,71</t>
+          <t>-4,17; 1,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,43</t>
+          <t>-5,9; -0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -1,31</t>
+          <t>-6,42; -1,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,96</t>
+          <t>-2,43; 1,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,04</t>
+          <t>-3,89; 0,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,66</t>
+          <t>-4,42; -0,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 76,42</t>
+          <t>-33,09; 83,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 51,72</t>
+          <t>-45,9; 51,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 48,5</t>
+          <t>-54,1; 41,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 29,63</t>
+          <t>-49,19; 37,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,79; -6,4</t>
+          <t>-67,6; -3,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,94; -23,52</t>
+          <t>-74,75; -25,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 34,52</t>
+          <t>-33,09; 32,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 1,12</t>
+          <t>-51,35; 0,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -11,61</t>
+          <t>-57,92; -11,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 18,05</t>
+          <t>-0,44; 19,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 15,54</t>
+          <t>-4,79; 17,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 3,8</t>
+          <t>-9,66; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 1,98</t>
+          <t>-16,26; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 0,15</t>
+          <t>-17,75; 0,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 3,65</t>
+          <t>-16,38; 4,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 8,16</t>
+          <t>-5,83; 8,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 4,21</t>
+          <t>-9,67; 4,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 1,11</t>
+          <t>-11,13; 1,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 924,11</t>
+          <t>-32,6; 898,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-79,06; 1168,42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,02</t>
+          <t>-91,58; 143,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,46</t>
+          <t>-100,0; 222,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,83</t>
+          <t>-100,0; 153,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 172,97</t>
+          <t>-54,39; 176,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,31; 103,04</t>
+          <t>-87,48; 111,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-93,18; 44,78</t>
+          <t>-94,1; 88,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,89</t>
+          <t>-3,67; 4,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,95</t>
+          <t>-3,38; 3,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,56</t>
+          <t>-4,62; 2,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,67</t>
+          <t>-3,46; 3,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,53</t>
+          <t>-5,82; 0,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,08</t>
+          <t>-6,52; -0,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,24</t>
+          <t>-2,28; 2,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,1</t>
+          <t>-3,72; 1,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,03</t>
+          <t>-4,54; 0,14</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 85,5</t>
+          <t>-46,22; 92,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 69,42</t>
+          <t>-44,74; 84,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 57,18</t>
+          <t>-60,11; 67,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 72,45</t>
+          <t>-42,04; 81,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 31,41</t>
+          <t>-66,72; 21,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,86; 1,39</t>
+          <t>-75,37; -2,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 63,38</t>
+          <t>-30,79; 56,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 22,03</t>
+          <t>-48,41; 21,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; -0,24</t>
+          <t>-60,15; 3,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 0,76</t>
+          <t>-9,85; 0,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 3,62</t>
+          <t>-7,32; 3,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,84</t>
+          <t>-6,75; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 2,54</t>
+          <t>-9,02; 2,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 1,61</t>
+          <t>-9,54; 1,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 1,4</t>
+          <t>-8,89; 1,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 0,43</t>
+          <t>-6,91; 0,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 1,31</t>
+          <t>-6,57; 1,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 1,15</t>
+          <t>-6,01; 1,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,18</t>
+          <t>-100,0; 125,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 201,19</t>
+          <t>-86,98; 245,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,95; 162,68</t>
+          <t>-77,6; 195,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,92; 159,48</t>
+          <t>-90,47; 125,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,49</t>
+          <t>-100,0; 104,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,73; 97,95</t>
+          <t>-90,97; 129,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 24,29</t>
+          <t>-85,43; 24,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 47,42</t>
+          <t>-81,25; 38,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 52,32</t>
+          <t>-75,94; 58,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,65</t>
+          <t>-2,38; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,15</t>
+          <t>-3,13; 2,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,8</t>
+          <t>-3,75; 1,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,86</t>
+          <t>-4,42; 1,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,39</t>
+          <t>-6,0; -0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,56</t>
+          <t>-6,63; -1,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,68</t>
+          <t>-2,59; 1,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,02</t>
+          <t>-3,76; 0,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,68</t>
+          <t>-4,36; -0,63</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 83,34</t>
+          <t>-33,03; 91,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 51,23</t>
+          <t>-44,12; 57,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 41,55</t>
+          <t>-50,56; 44,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 37,15</t>
+          <t>-51,94; 30,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,6; -3,83</t>
+          <t>-69,38; -7,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,75; -25,44</t>
+          <t>-75,33; -20,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 32,03</t>
+          <t>-35,27; 27,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 0,23</t>
+          <t>-49,38; 2,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,92; -11,27</t>
+          <t>-58,21; -10,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,69</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,48</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,72</t>
+          <t>-4,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 19,39</t>
+          <t>-17,32; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 17,24</t>
+          <t>-17,43; 1,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 3,82</t>
+          <t>-15,83; 6,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 2,79</t>
+          <t>-1,23; 18,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 0,4</t>
+          <t>-5,65; 15,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 4,7</t>
+          <t>-9,58; 5,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 8,11</t>
+          <t>-5,72; 7,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 4,34</t>
+          <t>-8,93; 4,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 1,59</t>
+          <t>-10,66; 2,02</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-58,91%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-77,1%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-58,17%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>149,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>53,68%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-55,93%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-58,91%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-77,1%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-57,52%</t>
+          <t>-53,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-57,43%</t>
+          <t>-56,59%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 898,54</t>
+          <t>-100,0; 94,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,06; 1168,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 360,25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-34,89; 825,44</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-91,58; 143,59</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 222,64</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 176,65</t>
+          <t>-50,44; 155,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 111,83</t>
+          <t>-85,3; 111,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,1; 88,67</t>
+          <t>-94,83; 83,5</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,51</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,49</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,2</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 4,18</t>
+          <t>-3,41; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,22</t>
+          <t>-5,49; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,74</t>
+          <t>-6,67; -0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,86</t>
+          <t>-3,35; 4,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,99</t>
+          <t>-4,26; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -0,32</t>
+          <t>-5,21; 1,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,86</t>
+          <t>-2,42; 3,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,14</t>
+          <t>-4,95; -0,3</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-32,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-52,44%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-8,01%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-16,97%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-32,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-49,97%</t>
+          <t>-24,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-35,75%</t>
+          <t>-40,25%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 92,84</t>
+          <t>-41,2; 95,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 84,06</t>
+          <t>-65,43; 29,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 67,02</t>
+          <t>-75,97; -4,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 81,96</t>
+          <t>-45,24; 100,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,72; 21,13</t>
+          <t>-52,23; 65,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,37; -2,83</t>
+          <t>-63,71; 50,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 56,11</t>
+          <t>-32,14; 64,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 21,09</t>
+          <t>-48,22; 21,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 3,7</t>
+          <t>-62,23; -5,08</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,22</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,8</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,53</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,24</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 0,72</t>
+          <t>-9,18; 2,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,65</t>
+          <t>-9,09; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,9</t>
+          <t>-9,02; 1,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 2,24</t>
+          <t>-9,34; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 1,67</t>
+          <t>-7,56; 3,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 1,36</t>
+          <t>-6,68; 3,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,47</t>
+          <t>-6,72; 0,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,11</t>
+          <t>-6,79; 1,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 1,38</t>
+          <t>-5,85; 1,37</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-42,87%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-54,77%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-54,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-66,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-33,87%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-17,49%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-42,87%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-54,77%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-55,67%</t>
+          <t>-21,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-39,92%</t>
+          <t>-39,93%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 125,5</t>
+          <t>-93,4; 122,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,98; 245,35</t>
+          <t>-100,0; 155,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,6; 195,12</t>
+          <t>-89,55; 92,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,47; 125,09</t>
+          <t>-100,0; 171,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,94</t>
+          <t>-88,54; 185,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,97; 129,92</t>
+          <t>-79,66; 200,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,43; 24,37</t>
+          <t>-84,51; 18,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 38,39</t>
+          <t>-83,19; 50,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 58,26</t>
+          <t>-74,97; 49,36</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,95</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,57</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,68</t>
+          <t>-4,2; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,41</t>
+          <t>-5,93; -0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,74</t>
+          <t>-6,65; -1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,56</t>
+          <t>-2,42; 3,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,5</t>
+          <t>-3,16; 2,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -1,3</t>
+          <t>-4,16; 1,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,51</t>
+          <t>-2,47; 1,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,04</t>
+          <t>-4,08; 0,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,63</t>
+          <t>-4,5; -0,83</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-19,07%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-44,67%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-55,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-9,68%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-19,74%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-19,07%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-44,67%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,51%</t>
+          <t>-25,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-42,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 91,8</t>
+          <t>-48,69; 29,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 57,82</t>
+          <t>-69,79; -6,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 44,19</t>
+          <t>-75,65; -24,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 30,27</t>
+          <t>-33,59; 76,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -7,03</t>
+          <t>-44,75; 51,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,33; -20,99</t>
+          <t>-56,75; 33,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 27,65</t>
+          <t>-32,88; 34,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 2,17</t>
+          <t>-52,74; 1,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -10,17</t>
+          <t>-60,42; -14,97</t>
         </is>
       </c>
     </row>
